--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +2124,210 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122907445</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563023</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6504347</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122907436</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95128</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>563095</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6504315</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907445</v>
+        <v>122907436</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563023</v>
+        <v>563095</v>
       </c>
       <c r="R15" t="n">
-        <v>6504347</v>
+        <v>6504315</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B16" t="n">
-        <v>95128</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R16" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B15" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R15" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907445</v>
+        <v>122907436</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563023</v>
+        <v>563095</v>
       </c>
       <c r="R16" t="n">
-        <v>6504347</v>
+        <v>6504315</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907445</v>
+        <v>122907436</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563023</v>
+        <v>563095</v>
       </c>
       <c r="R15" t="n">
-        <v>6504347</v>
+        <v>6504315</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B16" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R16" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>122907436</v>
       </c>
       <c r="B15" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>122907436</v>
       </c>
       <c r="B15" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B15" t="n">
-        <v>95141</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R15" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907445</v>
+        <v>122907436</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>95147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563023</v>
+        <v>563095</v>
       </c>
       <c r="R16" t="n">
-        <v>6504347</v>
+        <v>6504315</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907445</v>
+        <v>122907436</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>95167</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563023</v>
+        <v>563095</v>
       </c>
       <c r="R15" t="n">
-        <v>6504347</v>
+        <v>6504315</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B16" t="n">
-        <v>95150</v>
+        <v>8445</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R16" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113349416</v>
+        <v>120779167</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
+        <v>91963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,50 +1610,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Bengölen, Ög</t>
+          <t>Skärlötamarken, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563027</v>
+        <v>562975</v>
       </c>
       <c r="R10" t="n">
-        <v>6504278</v>
+        <v>6504377</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,19 +1666,14 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>E-Nor-0739</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,26 +1688,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120779167</v>
+        <v>120779123</v>
       </c>
       <c r="B11" t="n">
-        <v>91963</v>
+        <v>90707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1712,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562975</v>
+        <v>563022</v>
       </c>
       <c r="R11" t="n">
-        <v>6504377</v>
+        <v>6504370</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1820,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120779123</v>
+        <v>120779180</v>
       </c>
       <c r="B12" t="n">
-        <v>90707</v>
+        <v>5169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,25 +1814,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563022</v>
+        <v>562996</v>
       </c>
       <c r="R12" t="n">
-        <v>6504370</v>
+        <v>6504388</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1922,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120779180</v>
+        <v>120779137</v>
       </c>
       <c r="B13" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562996</v>
+        <v>563022</v>
       </c>
       <c r="R13" t="n">
-        <v>6504388</v>
+        <v>6504370</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2024,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120779137</v>
+        <v>122907436</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>95167</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2022,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563022</v>
+        <v>563095</v>
       </c>
       <c r="R14" t="n">
-        <v>6504370</v>
+        <v>6504315</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,12 +2076,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122907436</v>
+        <v>122907445</v>
       </c>
       <c r="B15" t="n">
-        <v>95167</v>
+        <v>8445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2124,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563095</v>
+        <v>563023</v>
       </c>
       <c r="R15" t="n">
-        <v>6504315</v>
+        <v>6504347</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2225,108 +2207,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>122907445</v>
-      </c>
-      <c r="B16" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Skärlötamarken, Ög</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>563023</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6504347</v>
-      </c>
-      <c r="S16" t="n">
-        <v>15</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Kvillinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -1805,12 +1805,7 @@
         <v>120779180</v>
       </c>
       <c r="B12" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,6 +1831,15 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
@@ -1886,6 +1890,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1907,12 +1912,7 @@
         <v>120779137</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,6 +1938,15 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
@@ -1988,6 +1997,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2111,12 +2121,7 @@
         <v>122907445</v>
       </c>
       <c r="B15" t="n">
-        <v>8445</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,6 +2147,15 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skärlötamarken, Ög</t>
@@ -2192,6 +2206,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14507-2023 artfynd.xlsx
+++ b/artfynd/A 14507-2023 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>120779137</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>122907445</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
